--- a/0_Data/1_Parameter_Estimates/table_s1_r1.xlsx
+++ b/0_Data/1_Parameter_Estimates/table_s1_r1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alyssabilinsi/Brown Dropbox/Alyssa Bilinski/Apps/Overleaf/Sins_of_Omission/0_Data/1_Parameter_Estimates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8E3E7C-619A-564A-89CB-0C9CEFA57620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ABADBC-857B-B943-A493-08EC351355C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="760" windowWidth="28040" windowHeight="17440" xr2:uid="{C8B9D815-F331-A74D-8293-32420ADD3176}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="141">
   <si>
     <t>Thalidomide</t>
   </si>
@@ -448,10 +448,19 @@
     <t>\citep{gadsby_prospective_1993, lacroix_nausea_2000, louik_nausea_2006}</t>
   </si>
   <si>
-    <t>Gadsby: '=84-39 Lacroix: 45 days for group with continuous (severe nausea)</t>
-  </si>
-  <si>
     <t>1993_Gadsby.pdf; 2000_Lacroix.pdf</t>
+  </si>
+  <si>
+    <t>Percentage of women 15-49 with HIV on ART</t>
+  </si>
+  <si>
+    <t>https://www.dropbox.com/scl/fi/svvaxtji649lp1ugnakj1/2022_WHO_HIV_Preg.pdf?rlkey=2koje8etvcqgjglz0d5s68m7v&amp;dl=0</t>
+  </si>
+  <si>
+    <t>DTG.perc.preg.ART</t>
+  </si>
+  <si>
+    <t>Gadsby: 84-39 Lacroix: 45 days for group with continuous (severe nausea)</t>
   </si>
 </sst>
 </file>
@@ -821,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBEC417-9A54-6C48-AA4D-49133D95CEE3}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
@@ -1005,13 +1014,13 @@
         <v>135</v>
       </c>
       <c r="E9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F9" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1254,139 +1263,159 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="1">
+        <v>82</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>33</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>80</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F25" t="s">
         <v>41</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G25" t="s">
         <v>89</v>
       </c>
-      <c r="H24">
+      <c r="H25">
         <f>(0.9*16056+2.4*28110)/(16056+28110)</f>
         <v>1.8546936557532943</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="D25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" t="s">
-        <v>45</v>
-      </c>
-    </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>113</v>
+        <v>29</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1.2</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>110</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E28" t="s">
         <v>111</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F28" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>47</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C30" s="1">
         <v>8</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>48</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E30" t="s">
         <v>87</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F30" t="s">
         <v>50</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G30" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>134</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E31" t="s">
         <v>88</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F31" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
+    <row r="32" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>101</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E32" t="s">
         <v>94</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F32" t="s">
         <v>93</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>131</v>
       </c>
     </row>
